--- a/reports/excel/strings/low_performing_strings_report_22-05-2026.xlsx
+++ b/reports/excel/strings/low_performing_strings_report_22-05-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="low_performing_strings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'low_performing_strings'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'low_performing_strings'!$A$1:$M$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +31,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F9FE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF4D4D"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,13 +80,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,18 +541,4433 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NO LOW-PERFORMING STRINGS DETECTED</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BJC FOOD (MALAYSIA) SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>SHAH ALAM</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-1)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>NE=50476040</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>493.85</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>809.67</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>647.736</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A) total current is 39.01% lower than the highest string current for 100KTL-M1(COM1-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>BJC FOOD (MALAYSIA) SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>SHAH ALAM</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-1)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>NE=50476040</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>PV9 input current(A)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>602.36</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>809.67</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>647.736</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>PV9 input current(A) total current is 25.60% lower than the highest string current for 100KTL-M1(COM1-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>BJC FOOD (MALAYSIA) SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SHAH ALAM</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-1)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>NE=50476040</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>PV11 input current(A)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>510.48</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>809.67</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>647.736</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>PV11 input current(A) total current is 36.95% lower than the highest string current for 100KTL-M1(COM1-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BJC FOOD (MALAYSIA) SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SHAH ALAM</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-1)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>NE=50476040</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>PV13 input current(A)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>536.78</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>809.67</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>647.736</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>PV13 input current(A) total current is 33.70% lower than the highest string current for 100KTL-M1(COM1-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>BJC FOOD (MALAYSIA) SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SHAH ALAM</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-1)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>NE=50476040</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>PV15 input current(A)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>537.34</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>809.67</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>647.736</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>PV15 input current(A) total current is 33.63% lower than the highest string current for 100KTL-M1(COM1-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>BJC FOOD (MALAYSIA) SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SHAH ALAM</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-1)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>NE=50476040</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>PV17 input current(A)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>396.88</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>809.67</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>647.736</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>PV17 input current(A) total current is 50.98% lower than the highest string current for 100KTL-M1(COM1-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>BJC FOOD (MALAYSIA) SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SHAH ALAM</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-1)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>NE=50476040</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>457.93</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>809.67</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>647.736</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A) total current is 43.44% lower than the highest string current for 100KTL-M1(COM1-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-15)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412011</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>379.35</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>498.53</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>398.824</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 23.91% lower than the highest string current for 100KTL-M1(COM1-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-17)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412012</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>387.33</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>588.24</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>470.592</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 34.15% lower than the highest string current for 100KTL-M1(COM1-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-17)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412012</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>PV3 input current(A)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>418.34</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>588.24</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>470.592</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>PV3 input current(A) total current is 28.88% lower than the highest string current for 100KTL-M1(COM1-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-17)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412012</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>PV5 input current(A)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>429.61</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>588.24</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>470.592</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>PV5 input current(A) total current is 26.97% lower than the highest string current for 100KTL-M1(COM1-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-17)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412012</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>469.44</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>588.24</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>470.592</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A) total current is 20.20% lower than the highest string current for 100KTL-M1(COM1-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-17)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412012</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>390.85</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>588.24</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>470.592</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 33.56% lower than the highest string current for 100KTL-M1(COM1-17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-18)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412014</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>547.36</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>437.888</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 27.31% lower than the highest string current for 100KTL-M1(COM1-18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-18)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412014</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>PV11 input current(A)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>431.12</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>547.36</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>437.888</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>PV11 input current(A) total current is 21.24% lower than the highest string current for 100KTL-M1(COM1-18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-18)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412014</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>385.24</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>547.36</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>437.888</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 29.62% lower than the highest string current for 100KTL-M1(COM1-18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-19)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>NE=50411994</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>401.95</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>558.45</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>446.76</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 28.02% lower than the highest string current for 100KTL-M1(COM1-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-19)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>NE=50411994</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>PV3 input current(A)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>433.71</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>558.45</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>446.76</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>PV3 input current(A) total current is 22.34% lower than the highest string current for 100KTL-M1(COM1-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-19)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>NE=50411994</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>437.49</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>558.45</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>446.76</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A) total current is 21.66% lower than the highest string current for 100KTL-M1(COM1-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-19)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>NE=50411994</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>PV9 input current(A)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>438.09</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>558.45</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>446.76</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>PV9 input current(A) total current is 21.55% lower than the highest string current for 100KTL-M1(COM1-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-19)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>NE=50411994</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>384.95</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>558.45</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>446.76</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 31.07% lower than the highest string current for 100KTL-M1(COM1-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-20)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412016</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>410.4</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>554.88</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>443.904</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 26.04% lower than the highest string current for 100KTL-M1(COM1-20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>DSG MALAYSIA SDN. BHD</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>TELOK PANGLIMA GARANG</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>100KTL-M1(COM1-20)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NE=50412016</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>372.94</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>554.88</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>443.904</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 32.79% lower than the highest string current for 100KTL-M1(COM1-20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>KWANG HUA PERSENDIRIAN  METER  2-3-4-5-6</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>KLANG</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Block C - Inverter 7 - Meter 2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>NE=51163025</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>306.54</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>603.46</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>482.768</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 49.20% lower than the highest string current for Block C - Inverter 7 - Meter 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>KWANG HUA PERSENDIRIAN  METER  2-3-4-5-6</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>KLANG</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Block C - Inverter 7 - Meter 2</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>NE=51163025</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>PV3 input current(A)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>278.68</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>603.46</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>482.768</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>53.82</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>PV3 input current(A) total current is 53.82% lower than the highest string current for Block C - Inverter 7 - Meter 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 1</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003099</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>464.3</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>756.02</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>604.816</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 38.59% lower than the highest string current for Inverter 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003099</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>422.37</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>756.02</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>604.816</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 44.13% lower than the highest string current for Inverter 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003099</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>-50.33</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>756.02</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>604.816</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>106.66</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A) total current is 106.66% lower than the highest string current for Inverter 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 10</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003102</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>PV11 input current(A)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>472.15</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>774.16</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>619.328</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>PV11 input current(A) total current is 39.01% lower than the highest string current for Inverter 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 10</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003102</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>PV15 input current(A)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>500.96</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>774.16</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>619.328</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>PV15 input current(A) total current is 35.29% lower than the highest string current for Inverter 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003102</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>PV17 input current(A)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>774.16</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>619.328</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>PV17 input current(A) total current is 99.75% lower than the highest string current for Inverter 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003102</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>460.96</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>774.16</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>619.328</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A) total current is 40.46% lower than the highest string current for Inverter 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 10</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003102</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>PV6 input current(A)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>-10.13</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>774.16</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>619.328</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>101.31</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>PV6 input current(A) total current is 101.31% lower than the highest string current for Inverter 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 10</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003102</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>PV12 input current(A)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>457.51</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>774.16</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>619.328</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>PV12 input current(A) total current is 40.90% lower than the highest string current for Inverter 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 10</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003102</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>452.89</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>774.16</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>619.328</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A) total current is 41.50% lower than the highest string current for Inverter 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 10</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003102</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>PV20 input current(A)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>483.2</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>774.16</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>619.328</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>PV20 input current(A) total current is 37.58% lower than the highest string current for Inverter 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 2</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003098</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>494.01</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>725.24</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>580.192</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 31.88% lower than the highest string current for Inverter 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 2</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003098</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>417.06</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>725.24</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>580.192</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 42.49% lower than the highest string current for Inverter 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 3</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003101</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>458.28</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>717.0599999999999</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>573.648</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 36.09% lower than the highest string current for Inverter 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 3</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003101</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>423.93</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>717.0599999999999</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>573.648</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 40.88% lower than the highest string current for Inverter 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 3</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003101</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>717.0599999999999</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>573.648</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>100.78</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A) total current is 100.78% lower than the highest string current for Inverter 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 4</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003104</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A)</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>524.05</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>770.05</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>616.04</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A) total current is 31.95% lower than the highest string current for Inverter 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 4</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003104</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>PV9 input current(A)</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>501.33</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>770.05</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>616.04</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>PV9 input current(A) total current is 34.90% lower than the highest string current for Inverter 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 4</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003104</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>PV11 input current(A)</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>503.27</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>770.05</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>616.04</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>PV11 input current(A) total current is 34.64% lower than the highest string current for Inverter 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 4</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003104</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>PV8 input current(A)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>425.01</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>770.05</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>616.04</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>PV8 input current(A) total current is 44.81% lower than the highest string current for Inverter 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 4</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003104</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>PV10 input current(A)</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>446.64</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>770.05</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>616.04</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>PV10 input current(A) total current is 42.00% lower than the highest string current for Inverter 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 4</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003104</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>PV12 input current(A)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>463.43</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>770.05</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>616.04</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>PV12 input current(A) total current is 39.82% lower than the highest string current for Inverter 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 5</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003103</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>424.66</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>710.13</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>568.104</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 40.20% lower than the highest string current for Inverter 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 5</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003103</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>463.73</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>710.13</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>568.104</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 34.70% lower than the highest string current for Inverter 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 6</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003095</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>450.24</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>702.5700000000001</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>562.056</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 35.92% lower than the highest string current for Inverter 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 6</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003095</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>400.93</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>702.5700000000001</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>562.056</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>42.93</v>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 42.93% lower than the highest string current for Inverter 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 6</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003095</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A)</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>-14.88</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>702.5700000000001</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>562.056</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>102.12</v>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A) total current is 102.12% lower than the highest string current for Inverter 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 7</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003100</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>459.53</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>699.65</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>559.72</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 34.32% lower than the highest string current for Inverter 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 7</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003100</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>407.49</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>699.65</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>559.72</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 41.76% lower than the highest string current for Inverter 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 8</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003096</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A)</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>440.19</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>708.0599999999999</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>566.448</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A) total current is 37.83% lower than the highest string current for Inverter 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 8</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003096</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>PV6 input current(A)</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>-15.96</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>708.0599999999999</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>566.448</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>PV6 input current(A) total current is 102.25% lower than the highest string current for Inverter 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 8</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003096</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>PV20 input current(A)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>423.19</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>708.0599999999999</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>566.448</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>PV20 input current(A) total current is 40.23% lower than the highest string current for Inverter 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 9</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003097</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A)</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>463.72</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>782.46</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>625.968</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>PV1 input current(A) total current is 40.74% lower than the highest string current for Inverter 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 9</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003097</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>PV3 input current(A)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>444.11</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>782.46</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>625.968</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>PV3 input current(A) total current is 43.24% lower than the highest string current for Inverter 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 9</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003097</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A)</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>472.46</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>782.46</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>625.968</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>PV2 input current(A) total current is 39.62% lower than the highest string current for Inverter 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 9</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003097</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>PV4 input current(A)</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>506.58</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>782.46</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>625.968</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>PV4 input current(A) total current is 35.26% lower than the highest string current for Inverter 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>PKT 12 WAVES</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>PENANG</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Inverter 9</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>NE=56003097</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A)</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>-49.41</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>782.46</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>625.968</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>106.31</v>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A) total current is 106.31% lower than the highest string current for Inverter 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER _5 R1</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>NE=54942978</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>PV6 input current(A)</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>988.9299999999999</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>791.144</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>PV6 input current(A) total current is 101.50% lower than the highest string current for INVERTER _5 R1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER _5 R1</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>NE=54942978</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>PV12 input current(A)</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>-31.71</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>988.9299999999999</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>791.144</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>103.21</v>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>PV12 input current(A) total current is 103.21% lower than the highest string current for INVERTER _5 R1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER _5 R1</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>NE=54942978</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A)</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>-44.28</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>988.9299999999999</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>791.144</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>104.48</v>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A) total current is 104.48% lower than the highest string current for INVERTER _5 R1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_10</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679611</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>PV4 input current(A)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>833.33</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>666.664</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>PV4 input current(A) total current is 99.83% lower than the highest string current for INVERTER_10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_10</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679611</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>552.16</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>833.33</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>666.664</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A) total current is 33.74% lower than the highest string current for INVERTER_10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_10</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679611</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>PV8 input current(A)</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>536.99</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>833.33</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>666.664</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>PV8 input current(A) total current is 35.56% lower than the highest string current for INVERTER_10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_13</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679495</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A)</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>-20.72</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>888.49</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>710.792</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>102.33</v>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>PV16 input current(A) total current is 102.33% lower than the highest string current for INVERTER_13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_14</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679493</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>PV17 input current(A)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>791.62</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>1006.24</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>804.992</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>PV17 input current(A) total current is 21.33% lower than the highest string current for INVERTER_14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_14</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679493</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>716.83</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>1006.24</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>804.992</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A) total current is 28.76% lower than the highest string current for INVERTER_14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_15</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679053</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>PV4 input current(A)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>818.5599999999999</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>654.848</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>99.87</v>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>PV4 input current(A) total current is 99.87% lower than the highest string current for INVERTER_15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_7</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>NE=53676713</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>803.73</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>642.984</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>PV7 input current(A) total current is 97.67% lower than the highest string current for INVERTER_7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_9</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679667</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>537.98</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>877.52</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>702.016</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>PV19 input current(A) total current is 38.69% lower than the highest string current for INVERTER_9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>QL FOODS</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>TAIPING</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>INVERTER_9</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>NE=53679667</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>PV20 input current(A)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>490.12</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>877.52</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>702.016</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>PV20 input current(A) total current is 44.15% lower than the highest string current for INVERTER_9.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
-  </mergeCells>
+  <autoFilter ref="A1:M76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>